--- a/ECUControlPanel/data/ECU_Data.xlsx
+++ b/ECUControlPanel/data/ECU_Data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aybuk\Desktop\arayuz_qt_projeleri\proje1-ECU\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aybuk\Desktop\arayuz_qt_projeleri\proje1-ECU\ECUControlPanel\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECD31020-00C9-40AA-82D4-E4659E3203E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17EC222A-5B40-4EF4-BF02-A8610768761D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="64">
   <si>
     <t>RAM Address</t>
   </si>
@@ -205,13 +205,25 @@
   </si>
   <si>
     <t>Reserved / Buffer</t>
+  </si>
+  <si>
+    <t>Data Offset</t>
+  </si>
+  <si>
+    <t>x * 0.1</t>
+  </si>
+  <si>
+    <t>x * 0.01</t>
+  </si>
+  <si>
+    <t>x * 0.1 (Nm)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -234,6 +246,15 @@
       <family val="1"/>
       <charset val="162"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="162"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -255,7 +276,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
@@ -263,6 +284,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -543,676 +565,794 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="18.1328125" customWidth="1"/>
     <col min="2" max="2" width="21.59765625" customWidth="1"/>
     <col min="3" max="3" width="20.265625" customWidth="1"/>
     <col min="4" max="4" width="24.46484375" customWidth="1"/>
-    <col min="5" max="5" width="17.265625" customWidth="1"/>
+    <col min="5" max="5" width="21.46484375" customWidth="1"/>
+    <col min="6" max="6" width="20.265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="30" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" ht="15" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
       <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:6" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" s="2">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2">
+        <v>0</v>
+      </c>
+      <c r="C3" s="2">
+        <v>2</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A4" s="1">
         <v>4</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="A3" s="1">
-        <v>4</v>
-      </c>
-      <c r="B3" s="2">
-        <v>2</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="A4" s="1">
-        <v>6</v>
-      </c>
       <c r="B4" s="2">
         <v>2</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>5</v>
+      <c r="C4" s="2">
+        <v>2</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="F4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A5" s="1">
         <v>8</v>
       </c>
       <c r="B5" s="2">
+        <v>0</v>
+      </c>
+      <c r="C5" s="2">
         <v>1</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>5</v>
-      </c>
       <c r="D5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:6" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A6" s="1">
         <v>9</v>
       </c>
       <c r="B6" s="2">
+        <v>0</v>
+      </c>
+      <c r="C6" s="2">
         <v>1</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>5</v>
-      </c>
       <c r="D6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:6" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A7" s="1">
         <v>10</v>
       </c>
       <c r="B7" s="2">
-        <v>4</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>13</v>
+        <v>1</v>
+      </c>
+      <c r="C7" s="2">
+        <v>2</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:6" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A8" s="1">
         <v>14</v>
       </c>
       <c r="B8" s="2">
+        <v>0</v>
+      </c>
+      <c r="C8" s="2">
         <v>4</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:6" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A9" s="1">
         <v>18</v>
       </c>
       <c r="B9" s="2">
-        <v>2</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="C9" s="2">
+        <v>2</v>
       </c>
       <c r="D9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:6" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A10" s="1">
         <v>20</v>
       </c>
       <c r="B10" s="2">
-        <v>2</v>
-      </c>
-      <c r="C10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" s="2">
+        <v>2</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="E10" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:6" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A11" s="1">
+        <v>24</v>
+      </c>
+      <c r="B11" s="2">
+        <v>0</v>
+      </c>
+      <c r="C11" s="2">
+        <v>2</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A12" s="1">
+        <v>26</v>
+      </c>
+      <c r="B12" s="2">
+        <v>0</v>
+      </c>
+      <c r="C12" s="2">
+        <v>2</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="2">
-        <v>2</v>
-      </c>
-      <c r="C11" s="2" t="s">
+      <c r="F12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A13" s="1">
+        <v>28</v>
+      </c>
+      <c r="B13" s="2">
+        <v>2</v>
+      </c>
+      <c r="C13" s="2">
+        <v>2</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="A12" s="1">
+      <c r="E13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F13" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="2">
-        <v>2</v>
-      </c>
-      <c r="C12" s="2" t="s">
+    </row>
+    <row r="14" spans="1:6" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A14" s="1">
+        <v>32</v>
+      </c>
+      <c r="B14" s="2">
+        <v>0</v>
+      </c>
+      <c r="C14" s="2">
+        <v>2</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="A13" s="1">
+      <c r="E14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F14" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A15" s="1">
+        <v>34</v>
+      </c>
+      <c r="B15" s="2">
+        <v>0</v>
+      </c>
+      <c r="C15" s="2">
+        <v>2</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="2">
-        <v>2</v>
-      </c>
-      <c r="C13" s="2" t="s">
+      <c r="F15" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A16" s="1">
+        <v>36</v>
+      </c>
+      <c r="B16" s="2">
+        <v>1</v>
+      </c>
+      <c r="C16" s="2">
+        <v>2</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="E16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F16" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="A14" s="1">
+    <row r="17" spans="1:6" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A17" s="1">
+        <v>40</v>
+      </c>
+      <c r="B17" s="2">
+        <v>0</v>
+      </c>
+      <c r="C17" s="2">
+        <v>2</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B14" s="2">
-        <v>2</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E14" s="2" t="s">
+      <c r="F17" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="A15" s="1">
+    <row r="18" spans="1:6" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A18" s="1">
+        <v>42</v>
+      </c>
+      <c r="B18" s="2">
+        <v>2</v>
+      </c>
+      <c r="C18" s="2">
+        <v>2</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F18" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A19" s="1">
+        <v>46</v>
+      </c>
+      <c r="B19" s="2">
+        <v>0</v>
+      </c>
+      <c r="C19" s="2">
+        <v>4</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B15" s="2">
-        <v>2</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="A16" s="1">
+      <c r="F19" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A20" s="1">
+        <v>50</v>
+      </c>
+      <c r="B20" s="2">
+        <v>2</v>
+      </c>
+      <c r="C20" s="2">
+        <v>2</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B16" s="2">
-        <v>2</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="A17" s="1">
+      <c r="F20" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A21" s="1">
+        <v>54</v>
+      </c>
+      <c r="B21" s="2">
+        <v>0</v>
+      </c>
+      <c r="C21" s="2">
+        <v>4</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B17" s="2">
-        <v>2</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="A18" s="1">
+      <c r="F21" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A22" s="1">
+        <v>58</v>
+      </c>
+      <c r="B22" s="2">
+        <v>2</v>
+      </c>
+      <c r="C22" s="2">
+        <v>2</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F22" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A23" s="1">
+        <v>62</v>
+      </c>
+      <c r="B23" s="2">
+        <v>0</v>
+      </c>
+      <c r="C23" s="2">
+        <v>2</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B18" s="2">
+      <c r="F23" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A24" s="1">
+        <v>64</v>
+      </c>
+      <c r="B24" s="2">
+        <v>0</v>
+      </c>
+      <c r="C24" s="2">
+        <v>2</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F24" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A25" s="1">
+        <v>66</v>
+      </c>
+      <c r="B25" s="2">
+        <v>1</v>
+      </c>
+      <c r="C25" s="2">
+        <v>1</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F25" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A26" s="1">
+        <v>68</v>
+      </c>
+      <c r="B26" s="2">
+        <v>0</v>
+      </c>
+      <c r="C26" s="2">
         <v>4</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E18" s="2" t="s">
+      <c r="D26" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F26" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A27" s="1">
+        <v>72</v>
+      </c>
+      <c r="B27" s="2">
+        <v>0</v>
+      </c>
+      <c r="C27" s="2">
+        <v>1</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F27" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A28" s="1">
+        <v>73</v>
+      </c>
+      <c r="B28" s="2">
+        <v>0</v>
+      </c>
+      <c r="C28" s="2">
+        <v>1</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F28" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A29" s="1">
+        <v>74</v>
+      </c>
+      <c r="B29" s="2">
+        <v>1</v>
+      </c>
+      <c r="C29" s="2">
+        <v>2</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F29" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="A19" s="1">
-        <v>40</v>
-      </c>
-      <c r="B19" s="2">
+    <row r="30" spans="1:6" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A30" s="1">
+        <v>78</v>
+      </c>
+      <c r="B30" s="2">
+        <v>0</v>
+      </c>
+      <c r="C30" s="2">
         <v>4</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="A20" s="1">
-        <v>44</v>
-      </c>
-      <c r="B20" s="2">
-        <v>4</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="A21" s="1">
+      <c r="D30" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F30" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A31" s="1">
+        <v>82</v>
+      </c>
+      <c r="B31" s="2">
+        <v>0</v>
+      </c>
+      <c r="C31" s="2">
+        <v>2</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B21" s="2">
-        <v>4</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="A22" s="1">
+      <c r="F31" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A32" s="1">
+        <v>84</v>
+      </c>
+      <c r="B32" s="2">
+        <v>2</v>
+      </c>
+      <c r="C32" s="2">
+        <v>2</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F32" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A33" s="1">
+        <v>88</v>
+      </c>
+      <c r="B33" s="2">
+        <v>0</v>
+      </c>
+      <c r="C33" s="2">
+        <v>2</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F33" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A34" s="1">
+        <v>90</v>
+      </c>
+      <c r="B34" s="2">
+        <v>0</v>
+      </c>
+      <c r="C34" s="2">
+        <v>2</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E34" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B22" s="2">
-        <v>4</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="A23" s="1">
+      <c r="F34" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A35" s="1">
+        <v>92</v>
+      </c>
+      <c r="B35" s="2">
+        <v>0</v>
+      </c>
+      <c r="C35" s="2">
+        <v>2</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F35" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A36" s="1">
+        <v>94</v>
+      </c>
+      <c r="B36" s="2">
+        <v>0</v>
+      </c>
+      <c r="C36" s="2">
+        <v>2</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F36" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A37" s="1">
+        <v>96</v>
+      </c>
+      <c r="B37" s="2">
+        <v>0</v>
+      </c>
+      <c r="C37" s="2">
+        <v>2</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E37" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B23" s="2">
-        <v>4</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="A24" s="1">
-        <v>60</v>
-      </c>
-      <c r="B24" s="2">
-        <v>4</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="A25" s="1">
-        <v>64</v>
-      </c>
-      <c r="B25" s="2">
-        <v>2</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="A26" s="1">
-        <v>66</v>
-      </c>
-      <c r="B26" s="2">
-        <v>4</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="A27" s="1">
-        <v>70</v>
-      </c>
-      <c r="B27" s="2">
-        <v>1</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="A28" s="1">
-        <v>71</v>
-      </c>
-      <c r="B28" s="2">
-        <v>1</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="A29" s="1">
-        <v>72</v>
-      </c>
-      <c r="B29" s="2">
-        <v>2</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="A30" s="1">
-        <v>74</v>
-      </c>
-      <c r="B30" s="2">
-        <v>4</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="A31" s="1">
-        <v>78</v>
-      </c>
-      <c r="B31" s="2">
-        <v>2</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="A32" s="1">
-        <v>80</v>
-      </c>
-      <c r="B32" s="2">
-        <v>2</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="A33" s="1">
-        <v>82</v>
-      </c>
-      <c r="B33" s="2">
-        <v>2</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="A34" s="1">
-        <v>84</v>
-      </c>
-      <c r="B34" s="2">
-        <v>2</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E34" s="2" t="s">
+      <c r="F37" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="A35" s="1">
-        <v>86</v>
-      </c>
-      <c r="B35" s="2">
-        <v>2</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="A36" s="1">
-        <v>88</v>
-      </c>
-      <c r="B36" s="2">
-        <v>2</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="A37" s="1">
-        <v>90</v>
-      </c>
-      <c r="B37" s="2">
-        <v>2</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:6" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A38" s="1">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="B38" s="2">
-        <v>4</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="C38" s="2">
+        <v>2</v>
       </c>
       <c r="D38" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E38" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E38" s="2" t="s">
+      <c r="F38" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:6" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A39" s="1">
         <v>96</v>
       </c>
       <c r="B39" s="2">
         <v>4</v>
       </c>
-      <c r="C39" s="2" t="s">
-        <v>5</v>
+      <c r="C39" s="2">
+        <v>4</v>
       </c>
       <c r="D39" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E39" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E39" s="2" t="s">
+      <c r="F39" s="2" t="s">
         <v>7</v>
       </c>
     </row>
